--- a/data/trans_dic/P55$nadie-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$nadie-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,32</t>
+          <t>0,92; 8,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,76</t>
+          <t>1,66; 11,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,72</t>
+          <t>1,16; 7,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,08; 11,16</t>
+          <t>3,91; 11,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,27</t>
+          <t>0,88; 5,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 10,76</t>
+          <t>3,3; 10,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,91</t>
+          <t>2,46; 5,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 9,1</t>
+          <t>3,54; 8,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,84</t>
+          <t>1,67; 6,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 8,21</t>
+          <t>2,93; 8,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,24</t>
+          <t>2,4; 5,38</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,5</t>
+          <t>0,0; 50,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,89</t>
+          <t>2,7; 16,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,41; 31,05</t>
+          <t>7,55; 33,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 12,22</t>
+          <t>2,17; 12,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,13</t>
+          <t>0,0; 32,37</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 22,47</t>
+          <t>4,69; 22,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,54</t>
+          <t>3,66; 11,94</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 34,74</t>
+          <t>4,08; 34,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,09</t>
+          <t>0,0; 34,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 30,93</t>
+          <t>3,8; 32,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,11</t>
+          <t>0,0; 28,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 24,28</t>
+          <t>4,66; 24,03</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 10,48</t>
+          <t>2,15; 10,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 10,18</t>
+          <t>1,4; 11,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 8,95</t>
+          <t>2,92; 8,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,35</t>
+          <t>3,71; 10,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,61</t>
+          <t>1,06; 4,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 12,54</t>
+          <t>5,28; 12,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,56</t>
+          <t>3,01; 6,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,5</t>
+          <t>3,77; 8,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,5</t>
+          <t>1,49; 5,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,55</t>
+          <t>3,82; 9,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,41</t>
+          <t>3,63; 6,47</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>910; 8572</t>
+          <t>943; 8841</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2063; 14601</t>
+          <t>2057; 14497</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6272</t>
+          <t>0; 5693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1278; 7535</t>
+          <t>1130; 6919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8402; 22975</t>
+          <t>8053; 22752</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2153; 13209</t>
+          <t>2195; 13259</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7255; 22451</t>
+          <t>6889; 22634</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6251; 15223</t>
+          <t>6337; 14849</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10897; 28113</t>
+          <t>10932; 27242</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6235; 21890</t>
+          <t>6263; 22541</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8295; 24799</t>
+          <t>8863; 25825</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8705; 18606</t>
+          <t>8544; 19125</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7164</t>
+          <t>0; 7202</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1999</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1614</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1170; 6837</t>
+          <t>1162; 7144</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2113</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3857; 16156</t>
+          <t>3928; 17441</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1180; 6679</t>
+          <t>1184; 6602</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 8342</t>
+          <t>0; 8963</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2124</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3276; 16832</t>
+          <t>3516; 16591</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3310; 11274</t>
+          <t>3576; 11665</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2177</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1154</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1565</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>610; 5253</t>
+          <t>617; 5254</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4871</t>
+          <t>0; 4003</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1603</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>553; 4327</t>
+          <t>532; 4510</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5049</t>
+          <t>0; 5905</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 1704</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2029</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1687; 7067</t>
+          <t>1357; 6995</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2765; 13269</t>
+          <t>2724; 13387</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2039; 14879</t>
+          <t>2040; 16193</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6503</t>
+          <t>0; 6573</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4729; 13940</t>
+          <t>4548; 13362</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8948; 23910</t>
+          <t>8557; 23850</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2126; 12740</t>
+          <t>2942; 12966</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13564; 33523</t>
+          <t>14120; 33383</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10005; 21397</t>
+          <t>9826; 20396</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13766; 33965</t>
+          <t>13473; 31810</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7203; 23237</t>
+          <t>6291; 22031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15700; 37119</t>
+          <t>14844; 35393</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17316; 30899</t>
+          <t>17484; 31214</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$nadie-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$nadie-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,58</t>
+          <t>0,99; 9,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,68</t>
+          <t>1,65; 12,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,09</t>
+          <t>0,0; 6,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 7,09</t>
+          <t>1,31; 6,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 11,05</t>
+          <t>4,09; 11,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,29</t>
+          <t>1,16; 5,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 10,85</t>
+          <t>3,36; 10,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,76</t>
+          <t>2,48; 5,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,82</t>
+          <t>3,48; 8,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,01</t>
+          <t>1,72; 6,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,55</t>
+          <t>2,8; 8,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,38</t>
+          <t>2,64; 5,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,76</t>
+          <t>0,0; 51,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 16,61</t>
+          <t>3,09; 18,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 33,51</t>
+          <t>8,29; 31,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 12,08</t>
+          <t>2,08; 11,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,37</t>
+          <t>0,0; 29,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 22,15</t>
+          <t>4,62; 22,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 11,94</t>
+          <t>3,37; 10,89</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 34,75</t>
+          <t>3,43; 29,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,59</t>
+          <t>0,0; 37,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 32,24</t>
+          <t>3,66; 28,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,2</t>
+          <t>0,0; 22,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 24,03</t>
+          <t>4,38; 22,81</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 10,58</t>
+          <t>2,12; 11,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,08</t>
+          <t>1,36; 10,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,58</t>
+          <t>2,88; 8,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,33</t>
+          <t>3,67; 10,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,69</t>
+          <t>0,83; 4,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 12,49</t>
+          <t>5,32; 12,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,25</t>
+          <t>3,02; 6,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,9</t>
+          <t>3,95; 9,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,21</t>
+          <t>1,53; 5,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,1</t>
+          <t>4,0; 9,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,47</t>
+          <t>3,64; 6,4</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>14258</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>943; 8841</t>
+          <t>1019; 9415</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2057; 14497</t>
+          <t>2048; 15044</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5693</t>
+          <t>0; 6280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1130; 6919</t>
+          <t>1362; 7156</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8053; 22752</t>
+          <t>8420; 23205</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2195; 13259</t>
+          <t>2898; 13499</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6889; 22634</t>
+          <t>7011; 22606</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6337; 14849</t>
+          <t>6870; 16394</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10932; 27242</t>
+          <t>10748; 27569</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6263; 22541</t>
+          <t>6442; 22931</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8863; 25825</t>
+          <t>8471; 25672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8544; 19125</t>
+          <t>10055; 21058</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>7294</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7202</t>
+          <t>0; 7274</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1162; 7144</t>
+          <t>1461; 8543</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3928; 17441</t>
+          <t>4315; 16277</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1184; 6602</t>
+          <t>1305; 7201</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 8963</t>
+          <t>0; 8262</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3516; 16591</t>
+          <t>3465; 16681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3576; 11665</t>
+          <t>3706; 11979</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3864</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>617; 5254</t>
+          <t>568; 4918</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4003</t>
+          <t>0; 4286</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>532; 4510</t>
+          <t>577; 4415</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5905</t>
+          <t>0; 4792</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1357; 6995</t>
+          <t>1415; 7371</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>25416</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2724; 13387</t>
+          <t>2680; 14318</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2040; 16193</t>
+          <t>1985; 15764</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6573</t>
+          <t>0; 5968</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4548; 13362</t>
+          <t>4829; 14914</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8557; 23850</t>
+          <t>8471; 23526</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2942; 12966</t>
+          <t>2292; 12936</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14120; 33383</t>
+          <t>14223; 33820</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9826; 20396</t>
+          <t>10720; 23101</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13473; 31810</t>
+          <t>14130; 32718</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6291; 22031</t>
+          <t>6466; 21855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14844; 35393</t>
+          <t>15546; 36057</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17484; 31214</t>
+          <t>19015; 33467</t>
         </is>
       </c>
     </row>
